--- a/P1.xlsx
+++ b/P1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhi\OneDrive\Desktop\25082026---.net-fullstack-AI-enabled-Developers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B556C0AE-58BF-4249-9599-C910C16FBD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF083B75-6700-4BDE-B049-733CFC003988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{0C1C27DE-3CB8-4105-A8D4-CDC54201A30B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
   <si>
     <t>BU</t>
   </si>
@@ -144,22 +144,44 @@
     <t>Kennan Pham</t>
   </si>
   <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>Banking, World Bank</t>
-  </si>
-  <si>
-    <t>Funds</t>
-  </si>
-  <si>
-    <t>ConED</t>
-  </si>
-  <si>
-    <t>Unum (Insurance)</t>
-  </si>
-  <si>
-    <t>Travellers - Insurance</t>
+    <t>P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Console </t>
+  </si>
+  <si>
+    <t>BankingAPP</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Assigned as Shopping APP, 
+But your develop the project based on your BU/Client - Presentation - 23rd</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Slot</t>
+  </si>
+  <si>
+    <t>3PM - 4PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FullStack </t>
+  </si>
+  <si>
+    <t>4PM-5PM</t>
+  </si>
+  <si>
+    <t>Group Project</t>
   </si>
 </sst>
 </file>
@@ -334,91 +356,91 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -734,291 +756,331 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D395A4D1-59DC-49A3-9F16-FE51806E8AC8}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="34.299999999999997" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="20.07421875" customWidth="1"/>
-    <col min="4" max="4" width="17.921875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.07421875" customWidth="1"/>
+    <col min="3" max="3" width="17.921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.69140625" customWidth="1"/>
+    <col min="9" max="9" width="12.23046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="67.69140625" customWidth="1"/>
+    <col min="11" max="11" width="36.61328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="34.299999999999997" customHeight="1" thickBot="1">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A2" s="13" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="24" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A3" s="14"/>
+      <c r="B3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="34.299999999999997" customHeight="1" thickBot="1">
+      <c r="A5" s="14"/>
+      <c r="B5" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A6" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="34.299999999999997" customHeight="1" thickBot="1">
+      <c r="A7" s="14"/>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A8" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="34.299999999999997" customHeight="1" thickBot="1">
+      <c r="A9" s="14"/>
+      <c r="B9" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="34.299999999999997" customHeight="1" thickBot="1">
+      <c r="A11" s="14"/>
+      <c r="B11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A12" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A13" s="14"/>
+      <c r="B13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A14" s="14"/>
+      <c r="B14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="F14" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A15" s="14"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="16"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="34.299999999999997" customHeight="1">
+      <c r="A16" s="14"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="16"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" ht="34.299999999999997" customHeight="1">
+      <c r="A17" s="14"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="16"/>
+      <c r="F17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" ht="34.299999999999997" customHeight="1" thickBot="1">
+      <c r="A18" s="14"/>
+      <c r="B18" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:10" ht="34.299999999999997" customHeight="1">
+      <c r="A19" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="34.299999999999997" customHeight="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" ht="34.299999999999997" customHeight="1">
+      <c r="A21" s="14"/>
+      <c r="B21" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="F21" s="4"/>
+      <c r="G21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A3" s="15"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="24"/>
-    </row>
-    <row r="4" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A4" s="15"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="24"/>
-    </row>
-    <row r="5" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A5" s="14"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="24"/>
-    </row>
-    <row r="6" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="I21" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A7" s="14"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="24"/>
-    </row>
-    <row r="8" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A8" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="24" t="s">
+      <c r="J21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="34.299999999999997" customHeight="1" thickBot="1">
+      <c r="A22" s="14"/>
+      <c r="B22" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="F22" s="3"/>
+      <c r="G22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A9" s="14"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="24"/>
-    </row>
-    <row r="10" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="24"/>
-    </row>
-    <row r="12" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A12" s="13" t="s">
+    <row r="23" spans="1:10" ht="34.299999999999997" customHeight="1">
+      <c r="A23" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="34.299999999999997" customHeight="1" thickBot="1">
+      <c r="A24" s="14"/>
+      <c r="B24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:10" ht="34.299999999999997" customHeight="1">
+      <c r="A25" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A13" s="15"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="24"/>
-    </row>
-    <row r="14" spans="1:4" ht="34.299999999999997" customHeight="1">
-      <c r="A14" s="15"/>
-      <c r="B14" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="24"/>
-    </row>
-    <row r="15" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A15" s="15"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="24"/>
-    </row>
-    <row r="16" spans="1:4" ht="34.299999999999997" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="24"/>
-    </row>
-    <row r="17" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="24"/>
-    </row>
-    <row r="18" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A18" s="14"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="24"/>
-    </row>
-    <row r="19" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A20" s="15"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="24"/>
-    </row>
-    <row r="21" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A21" s="15"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="24"/>
-    </row>
-    <row r="22" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A22" s="14"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="24"/>
-    </row>
-    <row r="23" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A23" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A24" s="14"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="24"/>
-    </row>
-    <row r="25" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
-      <c r="A25" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="34.299999999999997" customHeight="1" thickBot="1">
+    </row>
+    <row r="26" spans="1:10" ht="34.299999999999997" customHeight="1" thickBot="1">
       <c r="A26" s="14"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="6" t="s">
+      <c r="B26" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="24"/>
+      <c r="C26" s="16"/>
+      <c r="F26" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="F2:F5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B14:B15"/>
     <mergeCell ref="A12:A18"/>
-    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D18"/>
-    <mergeCell ref="D19:D22"/>
-    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C18"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="C23:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
